--- a/2022 data/excel_outputs/19_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/19_boothwise_data.xlsx
@@ -14,11 +14,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="467">
   <si>
     <t>AC 19 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -757,7 +835,13 @@
     <t>praa0vi0 aphjlgddh dvitiiy</t>
   </si>
   <si>
-    <t>###### ###### ###### ######## ######## ######</t>
+    <t>PRA0VI0 TRILOKAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KASAMAPUR GADHI PRATHAM KAKSH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KASAMAPUR GADHI PRATHAM KAKSH 2</t>
   </si>
   <si>
     <t>mdrsaa arbiyaa jmiiul uluum maujaa nejo sraay</t>
@@ -1337,8 +1421,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1354,7 +1446,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1362,12 +1454,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1666,91 +1776,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="F2" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="G2" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="H2" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="I2" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="J2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="K2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="L2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="M2" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="N2" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="O2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="P2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="Q2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="R2" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="S2" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="T2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="U2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="V2" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="W2" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="X2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="Y2" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="Z2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="AA2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1758,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>690</v>
@@ -1841,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>1027</v>
@@ -1924,7 +2112,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>1159</v>
@@ -2007,7 +2195,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>1101</v>
@@ -2090,7 +2278,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>1057</v>
@@ -2173,7 +2361,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>1022</v>
@@ -2256,7 +2444,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>390</v>
@@ -2339,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>432</v>
@@ -2422,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>682</v>
@@ -2505,7 +2693,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>721</v>
@@ -2588,7 +2776,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>895</v>
@@ -2671,7 +2859,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>1083</v>
@@ -2754,7 +2942,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>1036</v>
@@ -2837,7 +3025,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>1013</v>
@@ -2920,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>748</v>
@@ -3003,7 +3191,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>859</v>
@@ -3086,7 +3274,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>869</v>
@@ -3169,7 +3357,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>592</v>
@@ -3252,7 +3440,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>829</v>
@@ -3335,7 +3523,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>1004</v>
@@ -3418,7 +3606,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>1111</v>
@@ -3501,7 +3689,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>885</v>
@@ -3584,7 +3772,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>877</v>
@@ -3667,7 +3855,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>936</v>
@@ -3750,7 +3938,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>775</v>
@@ -3833,7 +4021,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>1217</v>
@@ -3916,7 +4104,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>1131</v>
@@ -3999,7 +4187,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>912</v>
@@ -4082,7 +4270,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>753</v>
@@ -4165,7 +4353,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>751</v>
@@ -4248,7 +4436,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>887</v>
@@ -4331,7 +4519,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>883</v>
@@ -4414,7 +4602,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>1078</v>
@@ -4497,7 +4685,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>718</v>
@@ -4580,7 +4768,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C37">
         <v>1030</v>
@@ -4663,7 +4851,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C38">
         <v>874</v>
@@ -4746,7 +4934,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>833</v>
@@ -4829,7 +5017,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40">
         <v>1097</v>
@@ -4912,7 +5100,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>654</v>
@@ -4995,7 +5183,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>737</v>
@@ -5078,7 +5266,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>840</v>
@@ -5161,7 +5349,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C44">
         <v>661</v>
@@ -5244,7 +5432,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C45">
         <v>971</v>
@@ -5327,7 +5515,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C46">
         <v>979</v>
@@ -5410,7 +5598,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>688</v>
@@ -5493,7 +5681,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C48">
         <v>912</v>
@@ -5576,7 +5764,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>1002</v>
@@ -5659,7 +5847,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C50">
         <v>998</v>
@@ -5742,7 +5930,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>1070</v>
@@ -5825,7 +6013,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>1124</v>
@@ -5908,7 +6096,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>439</v>
@@ -5991,7 +6179,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>954</v>
@@ -6074,7 +6262,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>783</v>
@@ -6157,7 +6345,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>783</v>
@@ -6240,7 +6428,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>763</v>
@@ -6323,7 +6511,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C58">
         <v>1169</v>
@@ -6406,7 +6594,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>1141</v>
@@ -6489,7 +6677,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>780</v>
@@ -6572,7 +6760,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>816</v>
@@ -6655,7 +6843,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>414</v>
@@ -6738,7 +6926,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C63">
         <v>741</v>
@@ -6821,7 +7009,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C64">
         <v>993</v>
@@ -6904,7 +7092,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>700</v>
@@ -6987,7 +7175,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C66">
         <v>883</v>
@@ -7070,7 +7258,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>723</v>
@@ -7153,7 +7341,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>1121</v>
@@ -7236,7 +7424,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>582</v>
@@ -7319,7 +7507,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>821</v>
@@ -7402,7 +7590,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>329</v>
@@ -7485,7 +7673,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>1128</v>
@@ -7568,7 +7756,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>1210</v>
@@ -7651,7 +7839,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C74">
         <v>1209</v>
@@ -7734,7 +7922,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C75">
         <v>630</v>
@@ -7817,7 +8005,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C76">
         <v>996</v>
@@ -7900,7 +8088,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>837</v>
@@ -7983,7 +8171,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>921</v>
@@ -8066,7 +8254,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C79">
         <v>1139</v>
@@ -8149,7 +8337,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C80">
         <v>496</v>
@@ -8232,7 +8420,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>378</v>
@@ -8315,7 +8503,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>456</v>
@@ -8398,7 +8586,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>1146</v>
@@ -8481,7 +8669,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>877</v>
@@ -8564,7 +8752,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C85">
         <v>688</v>
@@ -8647,7 +8835,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C86">
         <v>747</v>
@@ -8730,7 +8918,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>619</v>
@@ -8813,7 +9001,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C88">
         <v>557</v>
@@ -8896,7 +9084,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>929</v>
@@ -8979,7 +9167,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>404</v>
@@ -9062,7 +9250,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C91">
         <v>1146</v>
@@ -9145,7 +9333,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C92">
         <v>1097</v>
@@ -9228,7 +9416,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C93">
         <v>1123</v>
@@ -9311,7 +9499,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C94">
         <v>888</v>
@@ -9394,7 +9582,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="C95">
         <v>865</v>
@@ -9477,7 +9665,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>994</v>
@@ -9560,7 +9748,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>986</v>
@@ -9643,7 +9831,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C98">
         <v>577</v>
@@ -9726,7 +9914,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C99">
         <v>696</v>
@@ -9809,7 +9997,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C100">
         <v>628</v>
@@ -9892,7 +10080,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C101">
         <v>845</v>
@@ -9975,7 +10163,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C102">
         <v>842</v>
@@ -10058,7 +10246,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C103">
         <v>799</v>
@@ -10141,7 +10329,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C104">
         <v>767</v>
@@ -10224,7 +10412,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>736</v>
@@ -10307,7 +10495,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C106">
         <v>470</v>
@@ -10390,7 +10578,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C107">
         <v>870</v>
@@ -10473,7 +10661,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C108">
         <v>297</v>
@@ -10556,7 +10744,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>944</v>
@@ -10639,7 +10827,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>1002</v>
@@ -10722,7 +10910,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C111">
         <v>572</v>
@@ -10805,7 +10993,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C112">
         <v>686</v>
@@ -10888,7 +11076,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>1120</v>
@@ -10971,7 +11159,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C114">
         <v>1177</v>
@@ -11054,7 +11242,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C115">
         <v>951</v>
@@ -11137,7 +11325,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C116">
         <v>1146</v>
@@ -11220,7 +11408,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C117">
         <v>1152</v>
@@ -11303,7 +11491,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C118">
         <v>688</v>
@@ -11386,7 +11574,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C119">
         <v>934</v>
@@ -11469,7 +11657,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>662</v>
@@ -11552,7 +11740,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>623</v>
@@ -11635,7 +11823,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C122">
         <v>729</v>
@@ -11718,7 +11906,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C123">
         <v>652</v>
@@ -11801,7 +11989,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>1112</v>
@@ -11884,7 +12072,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C125">
         <v>994</v>
@@ -11967,7 +12155,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C126">
         <v>1212</v>
@@ -12050,7 +12238,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C127">
         <v>849</v>
@@ -12133,7 +12321,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C128">
         <v>348</v>
@@ -12216,7 +12404,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C129">
         <v>1178</v>
@@ -12299,7 +12487,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>945</v>
@@ -12382,7 +12570,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C131">
         <v>780</v>
@@ -12465,7 +12653,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C132">
         <v>893</v>
@@ -12548,7 +12736,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>824</v>
@@ -12631,7 +12819,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C134">
         <v>354</v>
@@ -12714,7 +12902,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C135">
         <v>1025</v>
@@ -12797,7 +12985,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C136">
         <v>632</v>
@@ -12880,7 +13068,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C137">
         <v>1031</v>
@@ -12963,7 +13151,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C138">
         <v>982</v>
@@ -13046,7 +13234,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C139">
         <v>775</v>
@@ -13129,7 +13317,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C140">
         <v>738</v>
@@ -13212,7 +13400,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>817</v>
@@ -13295,7 +13483,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C142">
         <v>1107</v>
@@ -13378,7 +13566,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C143">
         <v>448</v>
@@ -13461,7 +13649,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C144">
         <v>1002</v>
@@ -13544,7 +13732,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>1096</v>
@@ -13627,7 +13815,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="C146">
         <v>1193</v>
@@ -13710,7 +13898,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C147">
         <v>793</v>
@@ -13793,7 +13981,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C148">
         <v>895</v>
@@ -13876,7 +14064,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>870</v>
@@ -13959,7 +14147,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C150">
         <v>857</v>
@@ -14042,7 +14230,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>825</v>
@@ -14125,7 +14313,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C152">
         <v>1054</v>
@@ -14208,7 +14396,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>1089</v>
@@ -14291,7 +14479,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>545</v>
@@ -14374,7 +14562,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C155">
         <v>582</v>
@@ -14457,7 +14645,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C156">
         <v>645</v>
@@ -14540,7 +14728,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C157">
         <v>706</v>
@@ -14623,7 +14811,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="C158">
         <v>708</v>
@@ -14706,7 +14894,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>810</v>
@@ -14789,7 +14977,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C160">
         <v>1167</v>
@@ -14872,7 +15060,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>587</v>
@@ -14955,7 +15143,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C162">
         <v>625</v>
@@ -15038,7 +15226,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C163">
         <v>669</v>
@@ -15121,7 +15309,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C164">
         <v>695</v>
@@ -15204,7 +15392,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C165">
         <v>705</v>
@@ -15287,7 +15475,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C166">
         <v>528</v>
@@ -15370,7 +15558,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C167">
         <v>639</v>
@@ -15453,7 +15641,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C168">
         <v>614</v>
@@ -15536,7 +15724,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C169">
         <v>604</v>
@@ -15619,7 +15807,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C170">
         <v>614</v>
@@ -15702,7 +15890,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="C171">
         <v>526</v>
@@ -15785,7 +15973,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C172">
         <v>716</v>
@@ -15868,7 +16056,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C173">
         <v>767</v>
@@ -15951,7 +16139,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C174">
         <v>793</v>
@@ -16034,7 +16222,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C175">
         <v>734</v>
@@ -16117,7 +16305,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C176">
         <v>814</v>
@@ -16200,7 +16388,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C177">
         <v>757</v>
@@ -16283,7 +16471,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C178">
         <v>1083</v>
@@ -16366,7 +16554,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C179">
         <v>997</v>
@@ -16449,7 +16637,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C180">
         <v>754</v>
@@ -16532,7 +16720,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C181">
         <v>628</v>
@@ -16615,7 +16803,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C182">
         <v>659</v>
@@ -16698,7 +16886,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C183">
         <v>922</v>
@@ -16781,7 +16969,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C184">
         <v>495</v>
@@ -16864,7 +17052,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C185">
         <v>754</v>
@@ -16947,7 +17135,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C186">
         <v>1142</v>
@@ -17030,7 +17218,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C187">
         <v>843</v>
@@ -17113,7 +17301,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C188">
         <v>1000</v>
@@ -17196,7 +17384,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C189">
         <v>1015</v>
@@ -17279,7 +17467,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C190">
         <v>696</v>
@@ -17362,7 +17550,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C191">
         <v>852</v>
@@ -17445,7 +17633,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C192">
         <v>1074</v>
@@ -17528,7 +17716,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C193">
         <v>1118</v>
@@ -17611,7 +17799,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C194">
         <v>797</v>
@@ -17694,7 +17882,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C195">
         <v>1177</v>
@@ -17777,7 +17965,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C196">
         <v>505</v>
@@ -17860,7 +18048,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C197">
         <v>1064</v>
@@ -17943,7 +18131,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C198">
         <v>784</v>
@@ -18026,7 +18214,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C199">
         <v>1024</v>
@@ -18109,7 +18297,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C200">
         <v>1045</v>
@@ -18192,7 +18380,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C201">
         <v>657</v>
@@ -18275,7 +18463,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="C202">
         <v>1026</v>
@@ -18358,7 +18546,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C203">
         <v>879</v>
@@ -18441,7 +18629,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="C204">
         <v>959</v>
@@ -18524,7 +18712,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C205">
         <v>622</v>
@@ -18607,7 +18795,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C206">
         <v>591</v>
@@ -18690,7 +18878,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C207">
         <v>468</v>
@@ -18773,7 +18961,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="C208">
         <v>277</v>
@@ -18856,7 +19044,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C209">
         <v>867</v>
@@ -18939,7 +19127,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C210">
         <v>766</v>
@@ -19022,7 +19210,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="C211">
         <v>878</v>
@@ -19105,7 +19293,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C212">
         <v>938</v>
@@ -19188,7 +19376,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C213">
         <v>856</v>
@@ -19271,7 +19459,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="C214">
         <v>815</v>
@@ -19354,7 +19542,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>962</v>
@@ -19437,7 +19625,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C216">
         <v>715</v>
@@ -19520,7 +19708,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C217">
         <v>1030</v>
@@ -19603,7 +19791,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C218">
         <v>1061</v>
@@ -19686,7 +19874,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="C219">
         <v>1000</v>
@@ -19769,7 +19957,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C220">
         <v>678</v>
@@ -19852,7 +20040,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>856</v>
@@ -19935,7 +20123,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C222">
         <v>376</v>
@@ -20018,7 +20206,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C223">
         <v>544</v>
@@ -20101,7 +20289,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C224">
         <v>1029</v>
@@ -20184,7 +20372,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C225">
         <v>613</v>
@@ -20267,7 +20455,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C226">
         <v>626</v>
@@ -20350,7 +20538,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C227">
         <v>520</v>
@@ -20433,7 +20621,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C228">
         <v>924</v>
@@ -20516,7 +20704,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C229">
         <v>897</v>
@@ -20599,7 +20787,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C230">
         <v>947</v>
@@ -20682,7 +20870,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>1201</v>
@@ -20765,7 +20953,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C232">
         <v>673</v>
@@ -20848,7 +21036,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>616</v>
@@ -20931,7 +21119,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C234">
         <v>917</v>
@@ -21014,7 +21202,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C235">
         <v>909</v>
@@ -21097,7 +21285,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C236">
         <v>917</v>
@@ -21180,7 +21368,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="C237">
         <v>1004</v>
@@ -21263,7 +21451,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C238">
         <v>904</v>
@@ -21346,7 +21534,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C239">
         <v>1046</v>
@@ -21429,7 +21617,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C240">
         <v>946</v>
@@ -21512,7 +21700,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C241">
         <v>924</v>
@@ -21595,7 +21783,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="C242">
         <v>1184</v>
@@ -21678,7 +21866,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="C243">
         <v>1228</v>
@@ -21761,7 +21949,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="C244">
         <v>1221</v>
@@ -21844,7 +22032,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C245">
         <v>821</v>
@@ -21927,7 +22115,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C246">
         <v>836</v>
@@ -22010,7 +22198,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C247">
         <v>1175</v>
@@ -22093,7 +22281,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C248">
         <v>792</v>
@@ -22176,7 +22364,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C249">
         <v>1159</v>
@@ -22259,7 +22447,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C250">
         <v>1104</v>
@@ -22342,7 +22530,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C251">
         <v>1057</v>
@@ -22425,7 +22613,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>1107</v>
@@ -22508,7 +22696,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>639</v>
@@ -22591,7 +22779,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>639</v>
@@ -22674,7 +22862,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>1189</v>
@@ -22757,7 +22945,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>1084</v>
@@ -22840,7 +23028,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>1087</v>
@@ -22923,7 +23111,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>1194</v>
@@ -23006,7 +23194,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>709</v>
@@ -23089,7 +23277,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>709</v>
@@ -23172,7 +23360,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>1112</v>
@@ -23255,7 +23443,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>1121</v>
@@ -23338,7 +23526,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>1191</v>
@@ -23421,7 +23609,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>1159</v>
@@ -23504,7 +23692,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>1060</v>
@@ -23587,7 +23775,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>1099</v>
@@ -23670,7 +23858,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>886</v>
@@ -23753,7 +23941,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>546</v>
@@ -23836,7 +24024,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>1013</v>
@@ -23919,7 +24107,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>1188</v>
@@ -24002,7 +24190,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>640</v>
@@ -24085,7 +24273,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>882</v>
@@ -24168,7 +24356,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>867</v>
@@ -24251,7 +24439,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>840</v>
@@ -24334,7 +24522,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>512</v>
@@ -24417,7 +24605,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>1048</v>
@@ -24500,7 +24688,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>773</v>
@@ -24583,7 +24771,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>979</v>
@@ -24666,7 +24854,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>734</v>
@@ -24749,7 +24937,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>510</v>
@@ -24832,7 +25020,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>633</v>
@@ -24915,7 +25103,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>1139</v>
@@ -24998,7 +25186,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>804</v>
@@ -25081,7 +25269,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>731</v>
@@ -25164,7 +25352,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>706</v>
@@ -25247,7 +25435,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>748</v>
@@ -25330,7 +25518,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>1154</v>
@@ -25413,7 +25601,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>1101</v>
@@ -25496,7 +25684,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>1124</v>
@@ -25579,7 +25767,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>1003</v>
@@ -25662,7 +25850,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>1002</v>
@@ -25745,7 +25933,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="C292">
         <v>1088</v>
@@ -25828,7 +26016,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C293">
         <v>933</v>
@@ -25911,7 +26099,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="C294">
         <v>976</v>
@@ -25994,7 +26182,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="C295">
         <v>1071</v>
@@ -26077,7 +26265,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="C296">
         <v>944</v>
@@ -26160,7 +26348,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="C297">
         <v>927</v>
@@ -26243,7 +26431,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="C298">
         <v>1181</v>
@@ -26326,7 +26514,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="C299">
         <v>1112</v>
@@ -26409,7 +26597,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="C300">
         <v>1117</v>
@@ -26492,7 +26680,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="C301">
         <v>1197</v>
@@ -26575,7 +26763,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C302">
         <v>886</v>
@@ -26658,7 +26846,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C303">
         <v>872</v>
@@ -26741,7 +26929,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="C304">
         <v>851</v>
@@ -26824,7 +27012,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="C305">
         <v>871</v>
@@ -26907,7 +27095,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="C306">
         <v>1132</v>
@@ -26990,7 +27178,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="C307">
         <v>986</v>
@@ -27073,7 +27261,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="C308">
         <v>830</v>
@@ -27156,7 +27344,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="C309">
         <v>412</v>
@@ -27239,7 +27427,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="C310">
         <v>617</v>
@@ -27322,7 +27510,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="C311">
         <v>800</v>
@@ -27405,7 +27593,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="C312">
         <v>1138</v>
@@ -27488,7 +27676,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="C313">
         <v>1036</v>
@@ -27571,7 +27759,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="C314">
         <v>948</v>
@@ -27654,7 +27842,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="C315">
         <v>887</v>
@@ -27737,7 +27925,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="C316">
         <v>939</v>
@@ -27820,7 +28008,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>913</v>
@@ -27903,7 +28091,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>666</v>
@@ -27986,7 +28174,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>1080</v>
@@ -28069,7 +28257,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>1131</v>
@@ -28152,7 +28340,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>1089</v>
@@ -28235,7 +28423,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>1180</v>
@@ -28318,7 +28506,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>779</v>
@@ -28401,7 +28589,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>724</v>
@@ -28484,7 +28672,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>741</v>
@@ -28567,7 +28755,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>715</v>
@@ -28650,7 +28838,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>996</v>
@@ -28733,7 +28921,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>1048</v>
@@ -28816,7 +29004,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>895</v>
@@ -28899,7 +29087,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>821</v>
@@ -28982,7 +29170,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>792</v>
@@ -29065,7 +29253,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>725</v>
@@ -29148,7 +29336,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>1115</v>
@@ -29231,7 +29419,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>995</v>
@@ -29314,7 +29502,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>717</v>
@@ -29397,7 +29585,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>950</v>
@@ -29480,7 +29668,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>733</v>
@@ -29563,7 +29751,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>395</v>
@@ -29646,7 +29834,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>718</v>
@@ -29729,7 +29917,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>1218</v>
@@ -29812,7 +30000,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>748</v>
@@ -29895,7 +30083,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>763</v>
@@ -29978,7 +30166,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>872</v>
@@ -30061,7 +30249,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>745</v>
@@ -30144,7 +30332,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>474</v>
@@ -30227,7 +30415,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>798</v>
@@ -30310,7 +30498,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>800</v>
@@ -30393,7 +30581,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>822</v>
@@ -30476,7 +30664,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>928</v>
@@ -30559,7 +30747,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>603</v>
@@ -30642,7 +30830,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>833</v>
@@ -30725,7 +30913,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>731</v>
@@ -30808,7 +30996,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>996</v>
@@ -30891,7 +31079,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>891</v>
@@ -30974,7 +31162,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>897</v>
@@ -31057,7 +31245,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>978</v>
@@ -31140,7 +31328,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>1091</v>
@@ -31223,7 +31411,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>441</v>
@@ -31306,7 +31494,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>743</v>
@@ -31389,7 +31577,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>767</v>
@@ -31472,7 +31660,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>965</v>
@@ -31555,7 +31743,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>1196</v>
@@ -31638,7 +31826,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>784</v>
@@ -31721,7 +31909,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>667</v>
@@ -31804,7 +31992,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>712</v>
@@ -31887,7 +32075,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>799</v>
@@ -31970,7 +32158,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>780</v>
@@ -32053,7 +32241,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>886</v>
@@ -32136,7 +32324,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>891</v>
@@ -32219,7 +32407,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>624</v>
@@ -32302,7 +32490,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>642</v>
@@ -32385,7 +32573,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>1114</v>
@@ -32468,7 +32656,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>1011</v>
@@ -32551,7 +32739,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>532</v>
@@ -32634,7 +32822,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>1068</v>
@@ -32717,7 +32905,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>1101</v>
@@ -32800,7 +32988,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>916</v>
@@ -32883,7 +33071,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>884</v>
@@ -32966,7 +33154,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>882</v>
@@ -33049,7 +33237,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>759</v>
@@ -33132,7 +33320,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>565</v>
@@ -33215,7 +33403,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>1206</v>
@@ -33298,7 +33486,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>1215</v>
@@ -33381,7 +33569,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>1208</v>
@@ -33464,7 +33652,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>1036</v>
@@ -33547,7 +33735,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>998</v>
@@ -33630,7 +33818,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>758</v>
@@ -33713,7 +33901,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>1094</v>
@@ -33796,7 +33984,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>805</v>
@@ -33879,7 +34067,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>1087</v>
@@ -33962,7 +34150,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>1253</v>
@@ -34045,7 +34233,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>1015</v>
@@ -34128,7 +34316,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>812</v>
@@ -34211,7 +34399,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>798</v>
@@ -34294,7 +34482,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>991</v>
@@ -34377,7 +34565,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="C396">
         <v>349</v>
@@ -34460,7 +34648,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C397">
         <v>777</v>
@@ -34543,7 +34731,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="C398">
         <v>854</v>
@@ -34626,7 +34814,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C399">
         <v>701</v>
@@ -34709,7 +34897,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="C400">
         <v>752</v>
@@ -34792,7 +34980,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>1057</v>
@@ -34875,7 +35063,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>985</v>
@@ -34958,7 +35146,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>438</v>
@@ -35041,7 +35229,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>956</v>
@@ -35124,7 +35312,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>1165</v>
@@ -35207,7 +35395,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>825</v>
@@ -35290,7 +35478,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>995</v>
@@ -35373,7 +35561,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>348</v>
@@ -35456,7 +35644,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>1154</v>
@@ -35539,7 +35727,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>992</v>
@@ -35622,7 +35810,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>611</v>
@@ -35705,7 +35893,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>611</v>
@@ -35788,7 +35976,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>711</v>
@@ -35871,7 +36059,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>555</v>
@@ -35954,7 +36142,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>1183</v>
@@ -36037,7 +36225,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>683</v>
@@ -36120,7 +36308,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>629</v>
